--- a/dash-config.xlsx
+++ b/dash-config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Technical\Simulation\pythonutils\dash-lineplot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Technical\Utilities\Python\dash-lineplot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B3D09C-742E-419E-9B7A-B3F480D57ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8644F5D6-DF67-4F7D-A352-91621705B806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2451" windowWidth="24694" windowHeight="13260" tabRatio="686" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="165" yWindow="240" windowWidth="17250" windowHeight="16552" tabRatio="686" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="header" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="181">
   <si>
     <t>Variable</t>
   </si>
@@ -484,6 +484,117 @@
   </si>
   <si>
     <t>CurrentSimTime</t>
+  </si>
+  <si>
+    <t>commonX</t>
+  </si>
+  <si>
+    <t>Density</t>
+  </si>
+  <si>
+    <t>compact</t>
+  </si>
+  <si>
+    <t>Added in the browser-only version:</t>
+  </si>
+  <si>
+    <t>True or False: tie every graph on this tab to one x scale, default False</t>
+  </si>
+  <si>
+    <t>Zoom, pan or autoscale any graph and all the others follow.</t>
+  </si>
+  <si>
+    <t>Click or rubber-band select on any graph and every box on the tab fills at that x.</t>
+  </si>
+  <si>
+    <t>Each box quotes its own nearest recorded sample; nothing is interpolated.</t>
+  </si>
+  <si>
+    <t>Only graphs on the same tab are linked, and only if the tab is Included.</t>
+  </si>
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Ordered state names for a text column, drawn as an enumeration</t>
+  </si>
+  <si>
+    <t>Comma separated here, a JSON list in a .json config: Cueing, Tracking</t>
+  </si>
+  <si>
+    <t>Default if not given: order of first appearance in the data</t>
+  </si>
+  <si>
+    <t>A value in the data but missing from the list is appended, never dropped</t>
+  </si>
+  <si>
+    <t>Datafile (on a yValue row)</t>
+  </si>
+  <si>
+    <t>Data file for this line only, overriding the sheet Datafile</t>
+  </si>
+  <si>
+    <t>This is how one tab carries signals recorded at different rates</t>
+  </si>
+  <si>
+    <t>Density (header sheet)</t>
+  </si>
+  <si>
+    <t>'compact' or 'comfortable', default 'compact'</t>
+  </si>
+  <si>
+    <t>compact removes the space between graphs and draws the title inside the plot</t>
+  </si>
+  <si>
+    <t>Multi-rate JSON data</t>
+  </si>
+  <si>
+    <t>A .json data file may hold named groups, one per sample rate</t>
+  </si>
+  <si>
+    <t>Select one by appending a fragment: data/run.json#gimbal_1ms</t>
+  </si>
+  <si>
+    <t>A plain list of samples still means one single-rate table, as before</t>
+  </si>
+  <si>
+    <t>Text columns</t>
+  </si>
+  <si>
+    <t>Plotted as enumerations: labels on the y axis, drawn as steps</t>
+  </si>
+  <si>
+    <t>Scale and Offset are ignored for an enumeration</t>
+  </si>
+  <si>
+    <t>Changed 2026-09-11:</t>
+  </si>
+  <si>
+    <t>Also opens a BLOCK: rows below it apply to the graphs below it</t>
+  </si>
+  <si>
+    <t>A second Height starts a new block, which may name its own Datafile</t>
+  </si>
+  <si>
+    <t>A block inherits xValue and xLabel from above if it does not set them</t>
+  </si>
+  <si>
+    <t>This is how one tab carries several data files at different rates</t>
+  </si>
+  <si>
+    <t>REMOVED. Had been disabled for some time. Use blocks and commonX instead.</t>
+  </si>
+  <si>
+    <t>REMOVED with the x-axis slider.</t>
+  </si>
+  <si>
+    <t>X range boxes</t>
+  </si>
+  <si>
+    <t>Beside each graph: type a start and an end, Apply to zoom, Reset to undo</t>
+  </si>
+  <si>
+    <t>Replaces the old slider. On a commonX tab it drives every graph on the tab.</t>
   </si>
 </sst>
 </file>
@@ -946,14 +1057,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.84375" style="19" customWidth="1"/>
-    <col min="2" max="2" width="78.15234375" customWidth="1"/>
+    <col min="1" max="1" width="14.86328125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="78.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -961,7 +1072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
@@ -969,7 +1080,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="20" t="s">
         <v>87</v>
       </c>
@@ -977,7 +1088,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="102" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A4" s="20" t="s">
         <v>86</v>
       </c>
@@ -985,12 +1096,20 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1002,20 +1121,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.3828125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="66.69140625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="18.3984375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="66.6640625" style="13" customWidth="1"/>
     <col min="3" max="3" width="11" style="13" customWidth="1"/>
-    <col min="4" max="7" width="9.15234375" style="1"/>
-    <col min="8" max="8" width="12.3828125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="9.15234375" style="1"/>
-    <col min="11" max="11" width="13.53515625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.84375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.15234375" style="1"/>
+    <col min="4" max="7" width="9.1328125" style="1"/>
+    <col min="8" max="8" width="12.3984375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="9.1328125" style="1"/>
+    <col min="11" max="11" width="13.53125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.86328125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1172,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
@@ -1071,7 +1190,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="17" t="s">
         <v>20</v>
       </c>
@@ -1089,7 +1208,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="17" t="s">
         <v>44</v>
       </c>
@@ -1107,7 +1226,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="17" t="s">
         <v>5</v>
       </c>
@@ -1125,7 +1244,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
@@ -1141,7 +1260,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="17" t="s">
         <v>3</v>
       </c>
@@ -1159,7 +1278,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="17" t="s">
         <v>45</v>
       </c>
@@ -1177,7 +1296,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
@@ -1205,7 +1324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
         <v>7</v>
       </c>
@@ -1235,7 +1354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="17" t="s">
         <v>7</v>
       </c>
@@ -1263,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="17" t="s">
         <v>7</v>
       </c>
@@ -1291,7 +1410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A13" s="9" t="s">
         <v>88</v>
       </c>
@@ -1300,7 +1419,7 @@
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="9" t="s">
         <v>89</v>
       </c>
@@ -1309,7 +1428,7 @@
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:12" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9" t="s">
         <v>107</v>
       </c>
@@ -1317,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9" t="s">
         <v>109</v>
       </c>
@@ -1325,9 +1444,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B17" s="21" t="b">
         <v>0</v>
@@ -1345,14 +1464,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="82" customWidth="1"/>
-    <col min="3" max="4" width="14.3046875" customWidth="1"/>
-    <col min="12" max="12" width="14.69140625" customWidth="1"/>
+    <col min="3" max="4" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1390,7 +1509,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1408,7 +1527,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1426,7 +1545,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -1446,7 +1565,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1464,7 +1583,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1601,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>45</v>
       </c>
@@ -1502,7 +1621,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1520,7 +1639,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1538,7 +1657,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1556,7 +1675,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -1574,7 +1693,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A12" s="9" t="s">
         <v>88</v>
       </c>
@@ -1582,7 +1701,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="9" t="s">
         <v>89</v>
       </c>
@@ -1590,7 +1709,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="9" t="s">
         <v>107</v>
       </c>
@@ -1598,7 +1717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="9" t="s">
         <v>109</v>
       </c>
@@ -1606,9 +1725,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B16" s="21" t="b">
         <v>0</v>
@@ -1622,15 +1741,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.15234375" customWidth="1"/>
+    <col min="1" max="1" width="14.1328125" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="4" width="13.84375" customWidth="1"/>
-    <col min="12" max="12" width="16.3046875" customWidth="1"/>
+    <col min="3" max="4" width="13.86328125" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1668,7 +1787,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1686,7 +1805,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1704,7 +1823,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -1724,7 +1843,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1742,7 +1861,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
@@ -1760,7 +1879,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -1778,7 +1897,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -1798,7 +1917,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1816,15 +1935,15 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="9" t="s">
         <v>107</v>
       </c>
       <c r="B10" s="21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="9" t="s">
         <v>109</v>
       </c>
@@ -1832,9 +1951,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B12" s="21" t="b">
         <v>0</v>
@@ -1848,14 +1967,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="26.84375" customWidth="1"/>
-    <col min="3" max="4" width="14.3046875" customWidth="1"/>
-    <col min="12" max="12" width="15.84375" customWidth="1"/>
+    <col min="2" max="2" width="26.86328125" customWidth="1"/>
+    <col min="3" max="4" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="15.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1893,7 +2012,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1911,7 +2030,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1929,7 +2048,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -1947,7 +2066,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1965,7 +2084,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
@@ -1983,7 +2102,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -2001,7 +2120,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -2019,7 +2138,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2039,7 +2158,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -2059,7 +2178,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -2079,7 +2198,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="9" t="s">
         <v>107</v>
       </c>
@@ -2087,7 +2206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="9" t="s">
         <v>109</v>
       </c>
@@ -2095,12 +2214,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B14" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2111,14 +2230,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="26.84375" customWidth="1"/>
-    <col min="3" max="5" width="14.3046875" customWidth="1"/>
-    <col min="12" max="12" width="15.53515625" customWidth="1"/>
+    <col min="2" max="2" width="26.86328125" customWidth="1"/>
+    <col min="3" max="5" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="15.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2156,7 +2275,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2174,7 +2293,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2192,7 +2311,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -2210,7 +2329,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -2228,7 +2347,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
@@ -2246,7 +2365,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -2264,7 +2383,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -2284,7 +2403,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2304,7 +2423,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -2324,7 +2443,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -2344,7 +2463,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
@@ -2366,7 +2485,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
@@ -2386,7 +2505,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>7</v>
       </c>
@@ -2406,15 +2525,15 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="9" t="s">
         <v>107</v>
       </c>
       <c r="B15" s="21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="9" t="s">
         <v>109</v>
       </c>
@@ -2422,9 +2541,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B17" s="21" t="b">
         <v>0</v>
@@ -2438,16 +2557,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.69140625" customWidth="1"/>
-    <col min="2" max="2" width="36.15234375" customWidth="1"/>
-    <col min="3" max="5" width="14.3046875" customWidth="1"/>
-    <col min="11" max="11" width="14.3046875" customWidth="1"/>
-    <col min="12" max="12" width="15.3046875" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.1328125" customWidth="1"/>
+    <col min="3" max="5" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2485,7 +2604,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2503,7 +2622,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2521,7 +2640,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -2539,7 +2658,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -2557,7 +2676,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
@@ -2575,7 +2694,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -2593,7 +2712,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -2611,7 +2730,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2635,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -2655,7 +2774,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -2675,7 +2794,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
@@ -2697,7 +2816,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
@@ -2717,7 +2836,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>7</v>
       </c>
@@ -2737,7 +2856,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,7 +2874,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -2773,7 +2892,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>7</v>
       </c>
@@ -2797,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
@@ -2817,7 +2936,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>7</v>
       </c>
@@ -2837,15 +2956,15 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="9" t="s">
         <v>107</v>
       </c>
       <c r="B20" s="21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="9" t="s">
         <v>109</v>
       </c>
@@ -2853,12 +2972,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B22" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2869,16 +2988,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.69140625" customWidth="1"/>
-    <col min="2" max="2" width="36.15234375" customWidth="1"/>
-    <col min="3" max="5" width="14.3046875" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.1328125" customWidth="1"/>
+    <col min="3" max="5" width="14.33203125" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="15.3046875" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2916,7 +3035,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2934,7 +3053,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2952,7 +3071,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -2972,7 +3091,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -2990,7 +3109,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
@@ -3008,7 +3127,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,7 +3145,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -3046,7 +3165,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -3070,7 +3189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -3090,7 +3209,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -3110,7 +3229,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
@@ -3132,7 +3251,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
@@ -3152,7 +3271,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>7</v>
       </c>
@@ -3172,7 +3291,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
@@ -3190,7 +3309,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -3210,7 +3329,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>7</v>
       </c>
@@ -3234,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
@@ -3254,7 +3373,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>7</v>
       </c>
@@ -3274,7 +3393,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="9" t="s">
         <v>107</v>
       </c>
@@ -3282,7 +3401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="9" t="s">
         <v>109</v>
       </c>
@@ -3290,12 +3409,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B22" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3305,33 +3424,33 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AMK55"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AMK85"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="70.3046875" style="7" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="1"/>
+    <col min="1" max="1" width="19.6640625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="70.33203125" style="7" customWidth="1"/>
+    <col min="3" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A1" s="6"/>
       <c r="B1" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A2" s="8"/>
       <c r="B2" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A3" s="9"/>
       <c r="B3" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
@@ -3339,7 +3458,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:1025" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1025" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
         <v>20</v>
       </c>
@@ -3347,7 +3466,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
         <v>44</v>
       </c>
@@ -3355,7 +3474,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -3363,13 +3482,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A9" s="31" t="s">
         <v>123</v>
       </c>
       <c r="B9" s="31"/>
     </row>
-    <row r="10" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A10" s="9" t="s">
         <v>129</v>
       </c>
@@ -3377,7 +3496,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A11" s="6" t="s">
         <v>3</v>
       </c>
@@ -3385,7 +3504,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A12" s="6" t="s">
         <v>45</v>
       </c>
@@ -3393,7 +3512,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
         <v>7</v>
       </c>
@@ -3401,7 +3520,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:1025" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1025" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9" t="s">
         <v>131</v>
       </c>
@@ -4432,7 +4551,7 @@
       <c r="AMJ15" s="28"/>
       <c r="AMK15" s="28"/>
     </row>
-    <row r="16" spans="1:1025" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1025" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="B16" s="27" t="s">
         <v>133</v>
@@ -5461,7 +5580,7 @@
       <c r="AMJ16" s="28"/>
       <c r="AMK16" s="28"/>
     </row>
-    <row r="17" spans="1:1025" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:1025" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="9"/>
       <c r="B17" s="27" t="s">
         <v>134</v>
@@ -6490,7 +6609,7 @@
       <c r="AMJ17" s="28"/>
       <c r="AMK17" s="28"/>
     </row>
-    <row r="18" spans="1:1025" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1025" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" s="9" t="s">
         <v>137</v>
       </c>
@@ -7521,7 +7640,7 @@
       <c r="AMJ18" s="28"/>
       <c r="AMK18" s="28"/>
     </row>
-    <row r="19" spans="1:1025" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1025" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="9"/>
       <c r="B19" s="27" t="s">
         <v>135</v>
@@ -8550,7 +8669,7 @@
       <c r="AMJ19" s="28"/>
       <c r="AMK19" s="28"/>
     </row>
-    <row r="20" spans="1:1025" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1025" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="26" t="s">
         <v>124</v>
       </c>
@@ -9581,7 +9700,7 @@
       <c r="AMJ20" s="28"/>
       <c r="AMK20" s="28"/>
     </row>
-    <row r="21" spans="1:1025" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:1025" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A21" s="26"/>
       <c r="B21" s="27" t="s">
         <v>142</v>
@@ -10610,7 +10729,7 @@
       <c r="AMJ21" s="28"/>
       <c r="AMK21" s="28"/>
     </row>
-    <row r="22" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A22" s="9" t="s">
         <v>52</v>
       </c>
@@ -10618,16 +10737,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A23" s="9"/>
       <c r="B23" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A24" s="9"/>
     </row>
-    <row r="25" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A25" s="9" t="s">
         <v>53</v>
       </c>
@@ -10635,13 +10754,13 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A26" s="9"/>
       <c r="B26" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A27" s="9" t="s">
         <v>102</v>
       </c>
@@ -10649,7 +10768,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
@@ -10657,10 +10776,10 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A29" s="9"/>
     </row>
-    <row r="30" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A30" s="9" t="s">
         <v>99</v>
       </c>
@@ -10668,10 +10787,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A31" s="9"/>
     </row>
-    <row r="32" spans="1:1025" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A32" s="9" t="s">
         <v>70</v>
       </c>
@@ -10679,47 +10798,47 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="9"/>
       <c r="B33" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="9"/>
       <c r="B34" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="9"/>
       <c r="B35" s="11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" s="9"/>
       <c r="B36" s="11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="9"/>
       <c r="B37" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="9"/>
       <c r="B38" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" s="9"/>
       <c r="B39" s="11"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="9" t="s">
         <v>68</v>
       </c>
@@ -10727,17 +10846,17 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" s="9"/>
       <c r="B41" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" s="9"/>
       <c r="B42" s="11"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" s="9" t="s">
         <v>67</v>
       </c>
@@ -10745,16 +10864,16 @@
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" s="9"/>
       <c r="B44" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="9"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" s="9" t="s">
         <v>88</v>
       </c>
@@ -10762,10 +10881,10 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="9"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" s="9" t="s">
         <v>89</v>
       </c>
@@ -10773,10 +10892,10 @@
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" s="9"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" s="9" t="s">
         <v>107</v>
       </c>
@@ -10784,10 +10903,10 @@
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" s="9"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52" s="9" t="s">
         <v>109</v>
       </c>
@@ -10795,7 +10914,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="9" t="s">
         <v>139</v>
       </c>
@@ -10803,13 +10922,183 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" spans="1:2" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="55" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A55" s="12" t="s">
         <v>83</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>153</v>
+      </c>
+      <c r="B63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>161</v>
+      </c>
+      <c r="B69" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B72" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B81" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>139</v>
+      </c>
+      <c r="B82" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>129</v>
+      </c>
+      <c r="B83" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>178</v>
+      </c>
+      <c r="B84" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B85" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
